--- a/data/trans_dic/P34B01_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P34B01_R-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más</t>
+          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,35; 53,76</t>
+          <t>41,16; 53,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,15; 72,45</t>
+          <t>61,21; 72,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,66; 83,43</t>
+          <t>69,42; 82,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,94; 51,85</t>
+          <t>39,9; 53,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,6; 72,69</t>
+          <t>61,49; 73,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,33; 80,37</t>
+          <t>72,16; 80,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,03; 50,71</t>
+          <t>42,41; 50,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,49; 71,23</t>
+          <t>63,91; 71,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72,2; 80,09</t>
+          <t>72,34; 80,21</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,05; 59,43</t>
+          <t>49,78; 59,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,59; 60,89</t>
+          <t>52,49; 61,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,15; 67,21</t>
+          <t>56,08; 67,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,66; 53,75</t>
+          <t>45,04; 54,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,77; 60,6</t>
+          <t>52,24; 60,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,11; 58,13</t>
+          <t>50,19; 58,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,33; 54,84</t>
+          <t>48,48; 55,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,12; 59,34</t>
+          <t>52,99; 59,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,87; 61,39</t>
+          <t>54,62; 61,36</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,4; 49,59</t>
+          <t>38,16; 49,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,38; 67,58</t>
+          <t>56,99; 67,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,62; 54,97</t>
+          <t>43,4; 54,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,3; 61,11</t>
+          <t>50,54; 61,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,27; 73,76</t>
+          <t>63,59; 73,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,94; 57,28</t>
+          <t>48,37; 57,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,84; 53,76</t>
+          <t>46,12; 54,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>62,13; 69,78</t>
+          <t>61,65; 69,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,87; 55,1</t>
+          <t>48,07; 54,99</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,07; 41,64</t>
+          <t>31,05; 40,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,67; 76,12</t>
+          <t>67,0; 76,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,94; 56,36</t>
+          <t>41,11; 56,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,39; 50,33</t>
+          <t>39,96; 50,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,58; 70,67</t>
+          <t>60,36; 70,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,15; 54,46</t>
+          <t>26,6; 55,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,3; 44,5</t>
+          <t>36,96; 44,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,92; 72,09</t>
+          <t>65,1; 72,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,98; 53,14</t>
+          <t>33,8; 53,11</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,27; 48,3</t>
+          <t>34,6; 48,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,34; 61,8</t>
+          <t>48,47; 61,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,81; 95,27</t>
+          <t>88,75; 95,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,08; 53,98</t>
+          <t>39,94; 53,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,77; 50,83</t>
+          <t>37,23; 50,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,41; 93,78</t>
+          <t>88,13; 93,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,12; 49,12</t>
+          <t>39,75; 49,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,67; 54,23</t>
+          <t>44,82; 54,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,54; 93,74</t>
+          <t>89,39; 93,73</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,77; 49,99</t>
+          <t>37,75; 49,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,68; 38,94</t>
+          <t>26,99; 39,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,2; 45,86</t>
+          <t>35,25; 45,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,79; 62,21</t>
+          <t>50,42; 62,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,28; 49,64</t>
+          <t>36,99; 49,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,39; 48,54</t>
+          <t>38,96; 48,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,77; 54,48</t>
+          <t>45,58; 54,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,63; 42,12</t>
+          <t>34,24; 42,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,44; 45,59</t>
+          <t>38,21; 45,64</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,49; 51,36</t>
+          <t>43,26; 50,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50,72; 58,69</t>
+          <t>50,37; 58,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,65; 72,33</t>
+          <t>63,5; 72,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51,28; 59,02</t>
+          <t>51,46; 59,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,28; 58,71</t>
+          <t>50,95; 59,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,9; 87,27</t>
+          <t>60,88; 86,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,42; 54,18</t>
+          <t>48,63; 54,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>52,0; 57,62</t>
+          <t>51,72; 57,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>64,33; 79,78</t>
+          <t>64,14; 81,87</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>36,46; 43,81</t>
+          <t>36,69; 43,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38,96; 46,19</t>
+          <t>39,29; 46,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,55; 74,31</t>
+          <t>24,85; 74,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39,12; 46,72</t>
+          <t>39,33; 46,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,0; 41,98</t>
+          <t>35,36; 42,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,86; 69,82</t>
+          <t>63,62; 69,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,14; 44,16</t>
+          <t>39,11; 44,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,12; 43,07</t>
+          <t>38,25; 43,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36,33; 70,64</t>
+          <t>38,43; 71,0</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42,75; 46,36</t>
+          <t>42,7; 46,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52,55; 55,84</t>
+          <t>52,44; 56,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45,47; 65,07</t>
+          <t>45,4; 65,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47,55; 51,04</t>
+          <t>47,76; 51,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51,75; 55,08</t>
+          <t>51,57; 55,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,4; 68,48</t>
+          <t>58,54; 69,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,82; 48,31</t>
+          <t>45,71; 48,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>52,55; 55,02</t>
+          <t>52,46; 54,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52,94; 64,75</t>
+          <t>53,76; 64,56</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más</t>
+          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>121395; 157831</t>
+          <t>120842; 158264</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179641; 212826</t>
+          <t>179805; 213944</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>216940; 259833</t>
+          <t>216193; 257201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111865; 148939</t>
+          <t>114598; 152279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>177842; 209869</t>
+          <t>177515; 210764</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>209166; 232396</t>
+          <t>208665; 233249</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>244140; 294507</t>
+          <t>246314; 296158</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>369785; 414888</t>
+          <t>372234; 417956</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>433660; 481033</t>
+          <t>434467; 481724</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>253037; 300435</t>
+          <t>251656; 300428</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>259299; 306005</t>
+          <t>263811; 307292</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>290342; 347544</t>
+          <t>289961; 348760</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>233065; 280517</t>
+          <t>235071; 282887</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>270788; 317006</t>
+          <t>273236; 318009</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>255929; 296876</t>
+          <t>256347; 296241</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>496592; 563396</t>
+          <t>498134; 566502</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>544861; 608652</t>
+          <t>543497; 609707</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>563978; 630929</t>
+          <t>561409; 630698</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>124444; 160681</t>
+          <t>123661; 160787</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>182806; 215291</t>
+          <t>181553; 215681</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137860; 173735</t>
+          <t>137155; 170723</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>171548; 208383</t>
+          <t>172351; 210718</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>212786; 248062</t>
+          <t>213866; 246756</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>167067; 199615</t>
+          <t>168576; 201098</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>304837; 357511</t>
+          <t>306752; 359431</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>406875; 456939</t>
+          <t>403722; 452182</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>318111; 366159</t>
+          <t>319476; 365403</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>116195; 155735</t>
+          <t>116134; 152647</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>246643; 281619</t>
+          <t>247874; 284193</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126240; 173781</t>
+          <t>126752; 172817</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>157097; 195775</t>
+          <t>155416; 194993</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>234631; 273689</t>
+          <t>233769; 271134</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>131909; 255165</t>
+          <t>124619; 259266</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>284575; 339492</t>
+          <t>281951; 339122</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>491597; 545907</t>
+          <t>492947; 547345</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>263990; 412814</t>
+          <t>262600; 412578</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72873; 102699</t>
+          <t>73561; 103306</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>102108; 130539</t>
+          <t>102369; 129606</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>158750; 170286</t>
+          <t>158637; 170650</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88012; 118535</t>
+          <t>87697; 118472</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>82557; 111098</t>
+          <t>81380; 109905</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>184129; 195326</t>
+          <t>183549; 195130</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>169088; 212304</t>
+          <t>171791; 211931</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>191989; 233096</t>
+          <t>192624; 232907</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>346520; 362777</t>
+          <t>345971; 362763</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>103472; 136964</t>
+          <t>103430; 135722</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>70200; 102453</t>
+          <t>71004; 103072</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94916; 123646</t>
+          <t>95057; 123255</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142235; 174199</t>
+          <t>141205; 174620</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>101817; 135564</t>
+          <t>101016; 134385</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>101257; 124788</t>
+          <t>100161; 125153</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>253587; 301838</t>
+          <t>252541; 300593</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>180339; 225872</t>
+          <t>183595; 227758</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>202459; 240124</t>
+          <t>201248; 240363</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>287852; 339919</t>
+          <t>286365; 337026</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>333032; 385359</t>
+          <t>330687; 384261</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>395572; 449523</t>
+          <t>394694; 450297</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>355823; 409494</t>
+          <t>357086; 410939</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>354467; 405879</t>
+          <t>352207; 410480</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>515129; 738232</t>
+          <t>514979; 731250</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>656470; 734583</t>
+          <t>659315; 734525</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>700923; 776616</t>
+          <t>697079; 774816</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>944005; 1170707</t>
+          <t>941176; 1201393</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>284065; 341342</t>
+          <t>285824; 340436</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>303363; 359592</t>
+          <t>305879; 363088</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>217331; 685867</t>
+          <t>229398; 687454</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>322307; 384866</t>
+          <t>324002; 387007</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>289132; 346806</t>
+          <t>292164; 347788</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>455557; 498074</t>
+          <t>453865; 498712</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>627459; 707824</t>
+          <t>626900; 711864</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>611718; 691224</t>
+          <t>613847; 690478</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>594498; 1156062</t>
+          <t>628966; 1161868</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1464067; 1587622</t>
+          <t>1462378; 1587521</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1783825; 1895308</t>
+          <t>1779993; 1901186</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1566737; 2242151</t>
+          <t>1564500; 2246886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1690974; 1815026</t>
+          <t>1698472; 1820255</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1834306; 1952199</t>
+          <t>1827756; 1954278</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2126557; 2493674</t>
+          <t>2131832; 2518286</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3198768; 3372382</t>
+          <t>3190779; 3370581</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3646571; 3818082</t>
+          <t>3639807; 3809963</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3752286; 4588831</t>
+          <t>3810020; 4575706</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B01_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P34B01_R-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,16; 53,91</t>
+          <t>40,64; 52,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,21; 72,83</t>
+          <t>61,32; 72,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,42; 82,58</t>
+          <t>73,45; 84,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39,9; 53,01</t>
+          <t>39,91; 52,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,49; 73,0</t>
+          <t>61,94; 72,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,16; 80,66</t>
+          <t>72,49; 80,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,41; 50,99</t>
+          <t>42,59; 50,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,91; 71,76</t>
+          <t>63,35; 71,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72,34; 80,21</t>
+          <t>74,5; 80,82</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,78; 59,43</t>
+          <t>49,49; 58,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,49; 61,14</t>
+          <t>51,71; 60,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,08; 67,45</t>
+          <t>56,8; 67,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,04; 54,21</t>
+          <t>44,57; 54,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,24; 60,8</t>
+          <t>51,75; 60,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,19; 58,0</t>
+          <t>49,95; 58,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,48; 55,14</t>
+          <t>48,83; 55,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,99; 59,45</t>
+          <t>53,46; 59,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,62; 61,36</t>
+          <t>54,99; 61,62</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,16; 49,62</t>
+          <t>38,55; 49,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,99; 67,7</t>
+          <t>57,59; 68,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,4; 54,02</t>
+          <t>43,88; 54,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,54; 61,79</t>
+          <t>50,08; 61,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,59; 73,37</t>
+          <t>63,53; 73,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,37; 57,7</t>
+          <t>48,26; 56,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,12; 54,04</t>
+          <t>46,19; 53,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61,65; 69,05</t>
+          <t>61,93; 69,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,07; 54,99</t>
+          <t>47,59; 54,65</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,05; 40,82</t>
+          <t>30,92; 41,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,0; 76,82</t>
+          <t>67,24; 76,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,11; 56,05</t>
+          <t>43,26; 57,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,96; 50,13</t>
+          <t>40,51; 50,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,36; 70,01</t>
+          <t>60,42; 70,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,6; 55,34</t>
+          <t>51,21; 60,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,96; 44,45</t>
+          <t>37,2; 44,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,1; 72,28</t>
+          <t>65,41; 72,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,8; 53,11</t>
+          <t>48,94; 57,09</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,6; 48,59</t>
+          <t>34,72; 48,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,47; 61,36</t>
+          <t>48,26; 61,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,75; 95,47</t>
+          <t>89,59; 95,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,94; 53,95</t>
+          <t>39,91; 53,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,23; 50,28</t>
+          <t>37,79; 50,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,13; 93,69</t>
+          <t>89,23; 94,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,75; 49,03</t>
+          <t>39,36; 49,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,82; 54,19</t>
+          <t>44,42; 54,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,39; 93,73</t>
+          <t>90,38; 94,09</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,75; 49,54</t>
+          <t>38,05; 50,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,99; 39,17</t>
+          <t>26,9; 38,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,25; 45,71</t>
+          <t>34,75; 44,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,42; 62,36</t>
+          <t>51,17; 62,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,99; 49,2</t>
+          <t>37,38; 49,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,96; 48,69</t>
+          <t>39,04; 48,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,58; 54,26</t>
+          <t>46,45; 54,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,24; 42,47</t>
+          <t>33,98; 42,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,21; 45,64</t>
+          <t>37,99; 44,97</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,26; 50,92</t>
+          <t>43,1; 51,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50,37; 58,53</t>
+          <t>50,27; 58,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,5; 72,45</t>
+          <t>65,14; 73,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51,46; 59,23</t>
+          <t>51,42; 59,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,95; 59,38</t>
+          <t>51,47; 59,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,88; 86,45</t>
+          <t>59,43; 65,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,63; 54,18</t>
+          <t>48,49; 54,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,72; 57,49</t>
+          <t>52,01; 57,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>64,14; 81,87</t>
+          <t>63,06; 68,59</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>36,69; 43,7</t>
+          <t>36,83; 44,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39,29; 46,63</t>
+          <t>39,46; 46,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,85; 74,48</t>
+          <t>70,82; 77,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39,33; 46,98</t>
+          <t>38,99; 46,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,36; 42,1</t>
+          <t>35,01; 42,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,62; 69,91</t>
+          <t>64,76; 70,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,11; 44,41</t>
+          <t>39,1; 44,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,25; 43,03</t>
+          <t>38,15; 43,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,43; 71,0</t>
+          <t>68,79; 73,22</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42,7; 46,35</t>
+          <t>42,89; 46,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52,44; 56,01</t>
+          <t>52,47; 55,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45,4; 65,21</t>
+          <t>63,82; 67,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47,76; 51,18</t>
+          <t>47,71; 51,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51,57; 55,13</t>
+          <t>51,73; 55,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,54; 69,15</t>
+          <t>61,12; 63,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,71; 48,28</t>
+          <t>45,71; 48,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>52,46; 54,91</t>
+          <t>52,55; 54,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53,76; 64,56</t>
+          <t>62,7; 65,07</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240359</t>
+          <t>252303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>220880</t>
+          <t>242145</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>461238</t>
+          <t>494448</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>120842; 158264</t>
+          <t>119304; 154825</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179805; 213944</t>
+          <t>180129; 212750</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>216193; 257201</t>
+          <t>234205; 268555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114598; 152279</t>
+          <t>114631; 151042</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>177515; 210764</t>
+          <t>178818; 209874</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>208665; 233249</t>
+          <t>228752; 253646</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>246314; 296158</t>
+          <t>247340; 295775</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>372234; 417956</t>
+          <t>368979; 414960</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>434467; 481724</t>
+          <t>472660; 512705</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>320850</t>
+          <t>329781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>275771</t>
+          <t>292484</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>596621</t>
+          <t>622264</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>251656; 300428</t>
+          <t>250176; 298116</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>263811; 307292</t>
+          <t>259902; 304507</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>289961; 348760</t>
+          <t>300638; 358133</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>235071; 282887</t>
+          <t>232574; 282350</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>273236; 318009</t>
+          <t>270673; 318001</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>256347; 296241</t>
+          <t>270869; 314576</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>498134; 566502</t>
+          <t>501653; 567847</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>543497; 609707</t>
+          <t>548363; 611684</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>561409; 630698</t>
+          <t>589254; 660276</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156447</t>
+          <t>156778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>184493</t>
+          <t>186586</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>340940</t>
+          <t>343365</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>123661; 160787</t>
+          <t>124926; 159861</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>181553; 215681</t>
+          <t>183448; 217172</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137155; 170723</t>
+          <t>138666; 172715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>172351; 210718</t>
+          <t>170771; 209151</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>213866; 246756</t>
+          <t>213660; 248699</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>168576; 201098</t>
+          <t>171683; 201588</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>306752; 359431</t>
+          <t>307216; 358971</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>403722; 452182</t>
+          <t>405570; 454048</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>319476; 365403</t>
+          <t>319709; 367089</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149874</t>
+          <t>184784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>204002</t>
+          <t>231326</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>353876</t>
+          <t>416109</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>116134; 152647</t>
+          <t>115628; 155862</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>247874; 284193</t>
+          <t>248758; 283855</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126752; 172817</t>
+          <t>159423; 211023</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155416; 194993</t>
+          <t>157564; 196091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>233769; 271134</t>
+          <t>234007; 272710</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>124619; 259266</t>
+          <t>212329; 250963</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>281951; 339122</t>
+          <t>283829; 338545</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>492947; 547345</t>
+          <t>495297; 548792</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>262600; 412578</t>
+          <t>383292; 447112</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165550</t>
+          <t>191527</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>189960</t>
+          <t>208717</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>355511</t>
+          <t>400243</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>73561; 103306</t>
+          <t>73830; 102903</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>102369; 129606</t>
+          <t>101943; 130210</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>158637; 170650</t>
+          <t>184258; 197086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87697; 118472</t>
+          <t>87634; 117714</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>81380; 109905</t>
+          <t>82597; 111087</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>183549; 195130</t>
+          <t>202399; 213553</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>171791; 211931</t>
+          <t>170122; 211874</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>192624; 232907</t>
+          <t>190932; 232275</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>345971; 362763</t>
+          <t>390867; 406921</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108885</t>
+          <t>107142</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>111940</t>
+          <t>114508</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>220825</t>
+          <t>221651</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>103430; 135722</t>
+          <t>104238; 137489</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71004; 103072</t>
+          <t>70785; 100534</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>95057; 123255</t>
+          <t>94061; 121237</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>141205; 174620</t>
+          <t>143286; 175016</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>101016; 134385</t>
+          <t>102095; 134215</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>100161; 125153</t>
+          <t>102971; 127697</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>252541; 300593</t>
+          <t>257349; 303593</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>183595; 227758</t>
+          <t>182234; 227724</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>201248; 240363</t>
+          <t>203041; 240345</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>424652</t>
+          <t>495696</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>602654</t>
+          <t>480909</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1027306</t>
+          <t>976605</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>286365; 337026</t>
+          <t>285278; 338979</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>330687; 384261</t>
+          <t>330038; 384379</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>394694; 450297</t>
+          <t>466081; 523407</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>357086; 410939</t>
+          <t>356774; 412091</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>352207; 410480</t>
+          <t>355823; 411029</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>514979; 731250</t>
+          <t>456679; 505826</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>659315; 734525</t>
+          <t>657364; 737174</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>697079; 774816</t>
+          <t>701081; 778028</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>941176; 1201393</t>
+          <t>935730; 1017789</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>498042</t>
+          <t>587880</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>478103</t>
+          <t>560994</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>976145</t>
+          <t>1148873</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>285824; 340436</t>
+          <t>286953; 344737</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>305879; 363088</t>
+          <t>307259; 363289</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>229398; 687454</t>
+          <t>560723; 611210</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>324002; 387007</t>
+          <t>321255; 380371</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>292164; 347788</t>
+          <t>289227; 349234</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>453865; 498712</t>
+          <t>536435; 585046</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>626900; 711864</t>
+          <t>626705; 706120</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>613847; 690478</t>
+          <t>612224; 691533</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>628966; 1161868</t>
+          <t>1114561; 1186257</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2064659</t>
+          <t>2305891</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2267802</t>
+          <t>2317668</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4332462</t>
+          <t>4623559</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1462378; 1587521</t>
+          <t>1468850; 1586102</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1779993; 1901186</t>
+          <t>1781020; 1895981</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1564500; 2246886</t>
+          <t>2243971; 2369034</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1698472; 1820255</t>
+          <t>1696677; 1819503</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1827756; 1954278</t>
+          <t>1833690; 1954092</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2131832; 2518286</t>
+          <t>2270890; 2373455</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3190779; 3370581</t>
+          <t>3190897; 3376370</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3639807; 3809963</t>
+          <t>3646552; 3812051</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3810020; 4575706</t>
+          <t>4534560; 4706158</t>
         </is>
       </c>
     </row>
